--- a/astro-site/public/dl/kit-tareas-hotel/13-mantenimiento.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/13-mantenimiento.xlsx
@@ -1,21 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ronda Diaria" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Semanal" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Mensual" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="HVAC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Fontanería" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Electricidad" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ronda Diaria" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HVAC" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontanería" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electricidad" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Ronda Diaria'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'HVAC'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Fontanería'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Electricidad'!$5:$5</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -23,7 +30,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="11">
+  <fonts count="12">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -85,6 +92,11 @@
       <color rgb="00999999"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -142,48 +154,59 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+  <cellXfs count="17">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <dxfs count="1">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C8E6C9"/>
+          <bgColor rgb="00C8E6C9"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -543,15 +566,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B11"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="80"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="80" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -559,6 +583,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -587,9 +612,7 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="B8" t="inlineStr"/>
-    </row>
+    <row r="8"/>
     <row r="9">
       <c r="B9" s="2" t="inlineStr">
         <is>
@@ -611,8 +634,25 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13">
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -621,18 +661,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -649,6 +689,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -825,6 +866,26 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(E6:E12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>COUNTIF(B6:B12,"?*")</f>
+        <v>7.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -848,12 +909,26 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -862,18 +937,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -890,6 +965,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1085,6 +1161,26 @@
       <c r="E13" s="12" t="n"/>
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="13" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>COUNTIF(E6:E13,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E14">
+        <f>COUNTIF(B6:B13,"?*")</f>
+        <v>8.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1108,12 +1204,26 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1122,18 +1232,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1150,6 +1260,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1345,6 +1456,26 @@
       <c r="E13" s="12" t="n"/>
       <c r="F13" s="11" t="n"/>
       <c r="G13" s="13" t="n"/>
+    </row>
+    <row r="14">
+      <c r="B14" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C14">
+        <f>COUNTIF(E6:E13,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E14">
+        <f>COUNTIF(B6:B13,"?*")</f>
+        <v>8.0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
@@ -1368,12 +1499,26 @@
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G13">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12 E13" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1382,18 +1527,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1410,6 +1555,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1567,6 +1713,26 @@
       <c r="E11" s="12" t="n"/>
       <c r="F11" s="11" t="n"/>
       <c r="G11" s="13" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>COUNTIF(E6:E11,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E12">
+        <f>COUNTIF(B6:B11,"?*")</f>
+        <v>6.0</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
@@ -1590,12 +1756,26 @@
     <mergeCell ref="A14:G14"/>
     <mergeCell ref="A13:G13"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G11">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1604,18 +1784,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1632,6 +1812,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1808,6 +1989,26 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(E6:E12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>COUNTIF(B6:B12,"?*")</f>
+        <v>7.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -1831,12 +2032,26 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1845,18 +2060,18 @@
   <sheetPr>
     <tabColor rgb="00FFF3E0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="5"/>
-    <col customWidth="1" max="2" min="2" width="45"/>
-    <col customWidth="1" max="3" min="3" width="14"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="12"/>
-    <col customWidth="1" max="6" min="6" width="12"/>
-    <col customWidth="1" max="7" min="7" width="15"/>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1873,6 +2088,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -2049,6 +2265,26 @@
       <c r="E12" s="12" t="n"/>
       <c r="F12" s="11" t="n"/>
       <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>COUNTIF(E6:E12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>COUNTIF(B6:B12,"?*")</f>
+        <v>7.0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
@@ -2072,11 +2308,25 @@
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
   </mergeCells>
+  <conditionalFormatting sqref="A6:G12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" showDropDown="0" showErrorMessage="0" showInputMessage="0" sqref="E6 E7 E8 E9 E10 E11 E12" type="list">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
       <formula1>"✓,✗,—"</formula1>
     </dataValidation>
   </dataValidations>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-tareas-hotel/13-mantenimiento.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/13-mantenimiento.xlsx
@@ -11,17 +11,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ronda Diaria" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Semanal" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HVAC" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontanería" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electricidad" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Trimestral y Anual" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="HVAC" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fontanería" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Electricidad" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Ronda Diaria'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Semanal'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Mensual'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'HVAC'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Fontanería'!$5:$5</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Electricidad'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Trimestral y Anual'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'HVAC'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="6">'Fontanería'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="7">'Electricidad'!$5:$5</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -98,7 +100,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -129,6 +131,16 @@
         <bgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF8E1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF3E0"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -156,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -192,6 +204,12 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -568,7 +586,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -594,7 +612,7 @@
     <row r="5">
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>▸ 6 checklists: ronda diaria, semanal, mensual, HVAC, fontanería, electricidad.</t>
+          <t>▸ 7 checklists: ronda diaria, semanal, mensual, trimestral y anual, HVAC, fontanería, electricidad.</t>
         </is>
       </c>
     </row>
@@ -636,9 +654,45 @@
     </row>
     <row r="12"/>
     <row r="13">
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Más allá del mes:</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>▸ La hoja «Trimestral y Anual» recoge lo que se CONTRATA y se pide por escrito en una inspección: DDD, conductos de extracción, legionela (RD 487/2022), analíticas de piscina y spa, extintores y BIE, instalación de gas, OCA de baja tensión, ascensores, RITE, simulacro de evacuación, residuos, pólizas, licencias y facturación.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>▸ La columna «Cadencia» ya trae la periodicidad legal o recomendada de cada revisión; anota en «Notas» el número de parte y la fecha de la siguiente.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>▸ La descalcificación de cafeteras y termos es mensual y va en la hoja «Mensual»; la limpieza diaria del grupo de café la hace quien usa la máquina, en 01 (buffet) y en 04 (lobby bar).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17"/>
+    <row r="18">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-tareas-hotel · info@aichef.pro</t>
         </is>
       </c>
     </row>
@@ -874,7 +928,7 @@
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(E6:E12,"✓")</f>
+        <f>COUNTIFS(B6:B12,"?*",E6:E12,"✓")-COUNTIFS(B6:B12,"Tarea",E6:E12,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -883,7 +937,7 @@
         </is>
       </c>
       <c r="E13">
-        <f>COUNTIF(B6:B12,"?*")</f>
+        <f>COUNTIF(B6:B12,"?*")-COUNTIF(B6:B12,"Tarea")-COUNTIF(E6:E12,"N/A")</f>
         <v>7.0</v>
       </c>
     </row>
@@ -915,8 +969,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1169,7 +1223,7 @@
         </is>
       </c>
       <c r="C14">
-        <f>COUNTIF(E6:E13,"✓")</f>
+        <f>COUNTIFS(B6:B13,"?*",E6:E13,"✓")-COUNTIFS(B6:B13,"Tarea",E6:E13,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -1178,7 +1232,7 @@
         </is>
       </c>
       <c r="E14">
-        <f>COUNTIF(B6:B13,"?*")</f>
+        <f>COUNTIF(B6:B13,"?*")-COUNTIF(B6:B13,"Tarea")-COUNTIF(E6:E13,"N/A")</f>
         <v>8.0</v>
       </c>
     </row>
@@ -1210,8 +1264,8 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1234,7 +1288,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1330,7 +1384,7 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Inspeccionar cubiertas, canalones y bajantes</t>
+          <t>Descalcificar las cafeteras y los termos de agua de todos los outlets (buffet, lobby bar, à la carte, room service) o contratar la revisión al SAT, y cambiar los filtros descalcificadores del agua de aporte — anota la fecha y el nº de parte</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1349,7 +1403,7 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Revisar estado de pintura exterior e interior (zonas de uso)</t>
+          <t>Inspeccionar cubiertas, canalones y bajantes</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1368,7 +1422,7 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Verificar puertas cortafuegos: cierre, retenedores, señalización</t>
+          <t>Revisar estado de pintura exterior e interior (zonas de uso)</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1387,7 +1441,7 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Probar grupo electrógeno bajo carga (test mensual obligatorio)</t>
+          <t>Verificar puertas cortafuegos: cierre, retenedores, señalización</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1406,7 +1460,7 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Revisar fontanería: desagües, sifones, posibles fugas</t>
+          <t>Probar grupo electrógeno bajo carga (test mensual obligatorio)</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1425,7 +1479,7 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Inspeccionar mobiliario de habitaciones: cajones, bisagras, tiradores</t>
+          <t>Revisar fontanería: desagües, sifones, posibles fugas</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1444,12 +1498,12 @@
       </c>
       <c r="B13" s="9" t="inlineStr">
         <is>
-          <t>Actualizar registro de mantenimiento y planificar mes siguiente</t>
-        </is>
-      </c>
-      <c r="C13" s="15" t="inlineStr">
-        <is>
-          <t>Admin</t>
+          <t>Inspeccionar mobiliario de habitaciones: cajones, bisagras, tiradores</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
         </is>
       </c>
       <c r="D13" s="11" t="n"/>
@@ -1458,34 +1512,53 @@
       <c r="G13" s="13" t="n"/>
     </row>
     <row r="14">
-      <c r="B14" s="16" t="inlineStr">
+      <c r="A14" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Actualizar registro de mantenimiento y planificar mes siguiente</t>
+        </is>
+      </c>
+      <c r="C14" s="15" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="11" t="n"/>
+      <c r="G14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="B15" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C14">
-        <f>COUNTIF(E6:E13,"✓")</f>
+      <c r="C15">
+        <f>COUNTIFS(B6:B14,"?*",E6:E14,"✓")-COUNTIFS(B6:B14,"Tarea",E6:E14,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D14" t="inlineStr">
+      <c r="D15" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E14">
-        <f>COUNTIF(B6:B13,"?*")</f>
-        <v>8.0</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
+      <c r="E15">
+        <f>COUNTIF(B6:B14,"?*")-COUNTIF(B6:B14,"Tarea")-COUNTIF(E6:E14,"N/A")</f>
+        <v>9.0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="14" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -1494,19 +1567,19 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A17:G17"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A16:G16"/>
     <mergeCell ref="A2:G2"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G13">
+  <conditionalFormatting sqref="A6:G14">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12 E13 E14" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1529,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1544,7 +1617,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>HVAC — Climatización y Ventilación</t>
+          <t>Mantenimiento Trimestral y Anual — Revisiones Contratadas</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1632,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Control de climatización</t>
+          <t>Higiene alimentaria y control de plagas</t>
         </is>
       </c>
     </row>
@@ -1591,7 +1664,7 @@
       </c>
       <c r="F5" s="7" t="inlineStr">
         <is>
-          <t>Hora</t>
+          <t>Cadencia</t>
         </is>
       </c>
       <c r="G5" s="7" t="inlineStr">
@@ -1606,17 +1679,21 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Verificar consignas de temperatura por zona (habitaciones, lobby, salones)</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>HVAC</t>
+          <t>Control de plagas (DDD) de cocinas, almacenes y zonas comunes por empresa autorizada: visita, parte firmado y certificado en vigor</t>
+        </is>
+      </c>
+      <c r="C6" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
         </is>
       </c>
       <c r="D6" s="11" t="n"/>
       <c r="E6" s="12" t="n"/>
-      <c r="F6" s="11" t="n"/>
+      <c r="F6" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
       <c r="G6" s="13" t="n"/>
     </row>
     <row r="7">
@@ -1625,17 +1702,21 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Comprobar nivel de refrigerante en unidades de producción</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>HVAC</t>
+          <t>Limpieza de campanas y conductos de extracción de las cocinas por empresa homologada, con certificado</t>
+        </is>
+      </c>
+      <c r="C7" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
         </is>
       </c>
       <c r="D7" s="11" t="n"/>
       <c r="E7" s="12" t="n"/>
-      <c r="F7" s="11" t="n"/>
+      <c r="F7" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
       <c r="G7" s="13" t="n"/>
     </row>
     <row r="8">
@@ -1644,17 +1725,21 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Limpiar filtros de fancoils trimestral (rotar por plantas)</t>
-        </is>
-      </c>
-      <c r="C8" s="10" t="inlineStr">
-        <is>
-          <t>HVAC</t>
+          <t>Analítica de superficies, manipuladores y producto en laboratorio externo (verificación del plan de higiene)</t>
+        </is>
+      </c>
+      <c r="C8" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
         </is>
       </c>
       <c r="D8" s="11" t="n"/>
       <c r="E8" s="12" t="n"/>
-      <c r="F8" s="11" t="n"/>
+      <c r="F8" s="11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
       <c r="G8" s="13" t="n"/>
     </row>
     <row r="9">
@@ -1663,17 +1748,21 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Revisar termostatos: incidencias de habitaciones, calibración</t>
-        </is>
-      </c>
-      <c r="C9" s="10" t="inlineStr">
-        <is>
-          <t>HVAC</t>
+          <t>Revisar el plan APPCC y las fichas de proveedor: altas, bajas y cambios de carta y de buffet del año</t>
+        </is>
+      </c>
+      <c r="C9" s="18" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
       <c r="E9" s="12" t="n"/>
-      <c r="F9" s="11" t="n"/>
+      <c r="F9" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
       <c r="G9" s="13" t="n"/>
     </row>
     <row r="10">
@@ -1682,17 +1771,21 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Verificar ventilación y renovación de aire en zonas interiores</t>
-        </is>
-      </c>
-      <c r="C10" s="10" t="inlineStr">
-        <is>
-          <t>HVAC</t>
+          <t>Renovar la formación en manipulación de alimentos y en alérgenos de todo el personal de F&amp;B, extras incluidos</t>
+        </is>
+      </c>
+      <c r="C10" s="18" t="inlineStr">
+        <is>
+          <t>Admin</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
       <c r="E10" s="12" t="n"/>
-      <c r="F10" s="11" t="n"/>
+      <c r="F10" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
       <c r="G10" s="13" t="n"/>
     </row>
     <row r="11">
@@ -1701,69 +1794,648 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Registrar consumo energético y comparar con período anterior</t>
-        </is>
-      </c>
-      <c r="C11" s="10" t="inlineStr">
-        <is>
-          <t>HVAC</t>
+          <t>Calibrar termómetros y sondas de cámaras, buffet y room service contra un patrón conocido (agua con hielo, 0 °C) y anotar la desviación</t>
+        </is>
+      </c>
+      <c r="C11" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
         </is>
       </c>
       <c r="D11" s="11" t="n"/>
       <c r="E11" s="12" t="n"/>
-      <c r="F11" s="11" t="n"/>
+      <c r="F11" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
       <c r="G11" s="13" t="n"/>
     </row>
     <row r="12">
-      <c r="B12" s="16" t="inlineStr">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Agua, legionela, piscina y spa</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C13" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D13" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E13" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F13" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B14" s="9" t="inlineStr">
+        <is>
+          <t>Limpieza y desinfección de ACS, aljibes y torres de refrigeración por empresa autorizada, con certificado (plan de prevención de legionelosis, RD 487/2022)</t>
+        </is>
+      </c>
+      <c r="C14" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D14" s="11" t="n"/>
+      <c r="E14" s="12" t="n"/>
+      <c r="F14" s="11" t="inlineStr">
+        <is>
+          <t>Semestral</t>
+        </is>
+      </c>
+      <c r="G14" s="13" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B15" s="9" t="inlineStr">
+        <is>
+          <t>Analítica de legionela en laboratorio acreditado y registro en el libro de mantenimiento</t>
+        </is>
+      </c>
+      <c r="C15" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D15" s="11" t="n"/>
+      <c r="E15" s="12" t="n"/>
+      <c r="F15" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G15" s="13" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B16" s="9" t="inlineStr">
+        <is>
+          <t>Revisar la temperatura de ACS en puntos terminales (&gt; 50 °C) y purgar los de las habitaciones que llevan tiempo fuera de servicio</t>
+        </is>
+      </c>
+      <c r="C16" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="12" t="n"/>
+      <c r="F16" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G16" s="13" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B17" s="9" t="inlineStr">
+        <is>
+          <t>Analítica del agua de piscina y spa en laboratorio autorizado, además del control diario de cloro y pH</t>
+        </is>
+      </c>
+      <c r="C17" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="12" t="n"/>
+      <c r="F17" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B18" s="9" t="inlineStr">
+        <is>
+          <t>Vaciado, limpieza a fondo y revisión del vaso, la depuradora y las duchas de piscina y spa</t>
+        </is>
+      </c>
+      <c r="C18" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="12" t="n"/>
+      <c r="F18" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Instalaciones, incendios y seguridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C20" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D20" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E20" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F20" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B21" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de extintores, BIE y sistema de detección por empresa mantenedora autorizada (etiqueta y acta)</t>
+        </is>
+      </c>
+      <c r="C21" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D21" s="11" t="n"/>
+      <c r="E21" s="12" t="n"/>
+      <c r="F21" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B22" s="9" t="inlineStr">
+        <is>
+          <t>Retimbrado de extintores y prueba de presión de las BIE</t>
+        </is>
+      </c>
+      <c r="C22" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D22" s="11" t="n"/>
+      <c r="E22" s="12" t="n"/>
+      <c r="F22" s="11" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="G22" s="13" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B23" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de la instalación de gas de las cocinas por empresa habilitada, con certificado</t>
+        </is>
+      </c>
+      <c r="C23" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D23" s="11" t="n"/>
+      <c r="E23" s="12" t="n"/>
+      <c r="F23" s="11" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="G23" s="13" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B24" s="9" t="inlineStr">
+        <is>
+          <t>Inspección de la instalación eléctrica de baja tensión por OCA (organismo de control autorizado)</t>
+        </is>
+      </c>
+      <c r="C24" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D24" s="11" t="n"/>
+      <c r="E24" s="12" t="n"/>
+      <c r="F24" s="11" t="inlineStr">
+        <is>
+          <t>Cada 5 años</t>
+        </is>
+      </c>
+      <c r="G24" s="13" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B25" s="9" t="inlineStr">
+        <is>
+          <t>Inspección periódica de ascensores y montacargas por OCA, además del contrato de mantenimiento mensual</t>
+        </is>
+      </c>
+      <c r="C25" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D25" s="11" t="n"/>
+      <c r="E25" s="12" t="n"/>
+      <c r="F25" s="11" t="inlineStr">
+        <is>
+          <t>Cada 2 años</t>
+        </is>
+      </c>
+      <c r="G25" s="13" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B26" s="9" t="inlineStr">
+        <is>
+          <t>Revisión de la instalación térmica (RITE): calderas, enfriadoras y ACS, con el certificado de mantenimiento</t>
+        </is>
+      </c>
+      <c r="C26" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D26" s="11" t="n"/>
+      <c r="E26" s="12" t="n"/>
+      <c r="F26" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B27" s="9" t="inlineStr">
+        <is>
+          <t>Simulacro de evacuación y repaso del plan de autoprotección con todos los turnos</t>
+        </is>
+      </c>
+      <c r="C27" s="18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D27" s="11" t="n"/>
+      <c r="E27" s="12" t="n"/>
+      <c r="F27" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="B28" s="9" t="inlineStr">
+        <is>
+          <t>Retirada de residuos peligrosos y de aceite usado de cocina por gestor autorizado, y archivo del documento de entrega</t>
+        </is>
+      </c>
+      <c r="C28" s="17" t="inlineStr">
+        <is>
+          <t>Mantenimiento</t>
+        </is>
+      </c>
+      <c r="D28" s="11" t="n"/>
+      <c r="E28" s="12" t="n"/>
+      <c r="F28" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Documentación, seguros y personal</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C30" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D30" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E30" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F30" s="7" t="inlineStr">
+        <is>
+          <t>Cadencia</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B31" s="9" t="inlineStr">
+        <is>
+          <t>Revisar las pólizas de responsabilidad civil y de continente y contenido: sumas aseguradas, aforos y actividades cubiertas</t>
+        </is>
+      </c>
+      <c r="C31" s="18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="n"/>
+      <c r="E31" s="12" t="n"/>
+      <c r="F31" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B32" s="9" t="inlineStr">
+        <is>
+          <t>Archivar los registros de jornada del trimestre y revisar contratos y altas del personal eventual</t>
+        </is>
+      </c>
+      <c r="C32" s="18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D32" s="11" t="n"/>
+      <c r="E32" s="12" t="n"/>
+      <c r="F32" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G32" s="13" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B33" s="9" t="inlineStr">
+        <is>
+          <t>Revisión del PMS, del TPV y del software de facturación (requisitos antifraude / Verifactu)</t>
+        </is>
+      </c>
+      <c r="C33" s="18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D33" s="11" t="n"/>
+      <c r="E33" s="12" t="n"/>
+      <c r="F33" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G33" s="13" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B34" s="9" t="inlineStr">
+        <is>
+          <t>Renovar licencias y seguros obligatorios: actividad, ocupación, piscina y, si procede, terraza</t>
+        </is>
+      </c>
+      <c r="C34" s="18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D34" s="11" t="n"/>
+      <c r="E34" s="12" t="n"/>
+      <c r="F34" s="11" t="inlineStr">
+        <is>
+          <t>Anual</t>
+        </is>
+      </c>
+      <c r="G34" s="13" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B35" s="9" t="inlineStr">
+        <is>
+          <t>Actualizar escandallos, precios de carta y tarifas de banquete con los precios reales de proveedor</t>
+        </is>
+      </c>
+      <c r="C35" s="18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D35" s="11" t="n"/>
+      <c r="E35" s="12" t="n"/>
+      <c r="F35" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G35" s="13" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B36" s="9" t="inlineStr">
+        <is>
+          <t>Anotar en «Notas» el nº de parte de cada revisión y la fecha de la siguiente</t>
+        </is>
+      </c>
+      <c r="C36" s="18" t="inlineStr">
+        <is>
+          <t>Admin</t>
+        </is>
+      </c>
+      <c r="D36" s="11" t="n"/>
+      <c r="E36" s="12" t="n"/>
+      <c r="F36" s="11" t="inlineStr">
+        <is>
+          <t>Trimestral</t>
+        </is>
+      </c>
+      <c r="G36" s="13" t="n"/>
+    </row>
+    <row r="37">
+      <c r="B37" s="16" t="inlineStr">
         <is>
           <t>Tareas completadas:</t>
         </is>
       </c>
-      <c r="C12">
-        <f>COUNTIF(E6:E11,"✓")</f>
+      <c r="C37">
+        <f>COUNTIFS(B6:B36,"?*",E6:E36,"✓")-COUNTIFS(B6:B36,"Tarea",E6:E36,"✓")</f>
         <v>0.0</v>
       </c>
-      <c r="D12" t="inlineStr">
+      <c r="D37" t="inlineStr">
         <is>
           <t>de</t>
         </is>
       </c>
-      <c r="E12">
-        <f>COUNTIF(B6:B11,"?*")</f>
-        <v>6.0</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="14" t="inlineStr">
+      <c r="E37">
+        <f>COUNTIF(B6:B36,"?*")-COUNTIF(B6:B36,"Tarea")-COUNTIF(E6:E36,"N/A")</f>
+        <v>25.0</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="14" t="inlineStr">
         <is>
           <t>Firma responsable: _________________  Fecha: ___/___/______</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="14" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="14" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
+    <row r="40"/>
+    <row r="41"/>
+    <row r="42"/>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="8">
     <mergeCell ref="A4:G4"/>
     <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A14:G14"/>
-    <mergeCell ref="A13:G13"/>
+    <mergeCell ref="A39:G39"/>
+    <mergeCell ref="A19:G19"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A38:G38"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G11">
+  <conditionalFormatting sqref="A6:G36">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E14 E15 E16 E17 E18 E21 E22 E23 E24 E25 E26 E27 E28 E31 E32 E33 E34 E35 E36" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1786,7 +2458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -1801,7 +2473,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Fontanería — Control y Prevención</t>
+          <t>HVAC — Climatización y Ventilación</t>
         </is>
       </c>
     </row>
@@ -1816,7 +2488,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Revisiones de fontanería</t>
+          <t>Control de climatización</t>
         </is>
       </c>
     </row>
@@ -1863,12 +2535,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Verificar presión de agua en puntos altos del edificio</t>
+          <t>Verificar consignas de temperatura por zona (habitaciones, lobby, salones)</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Fontanería</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D6" s="11" t="n"/>
@@ -1882,12 +2554,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Controlar temperatura de ACS para prevención de legionella (&gt;50°C)</t>
+          <t>Comprobar nivel de refrigerante en unidades de producción</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Fontanería</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D7" s="11" t="n"/>
@@ -1901,12 +2573,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Inspeccionar cuartos técnicos: fugas, humedad, corrosión</t>
+          <t>Limpiar filtros de fancoils trimestral (rotar por plantas)</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Fontanería</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D8" s="11" t="n"/>
@@ -1920,12 +2592,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Realizar desatascos preventivos en zonas de alto uso</t>
+          <t>Revisar termostatos: incidencias de habitaciones, calibración</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Fontanería</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -1939,12 +2611,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Verificar cisternas: consumo fantasma, mecanismo, flotador</t>
+          <t>Verificar ventilación y renovación de aire en zonas interiores</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Fontanería</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -1958,12 +2630,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Revisar grifería de habitaciones: goteos, cal, funcionamiento</t>
+          <t>Registrar consumo energético y comparar con período anterior</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Fontanería</t>
+          <t>HVAC</t>
         </is>
       </c>
       <c r="D11" s="11" t="n"/>
@@ -1972,53 +2644,34 @@
       <c r="G11" s="13" t="n"/>
     </row>
     <row r="12">
-      <c r="A12" s="8" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="9" t="inlineStr">
-        <is>
-          <t>Verificar radiadores/calefacción: purgado, fugas, termostatos</t>
-        </is>
-      </c>
-      <c r="C12" s="10" t="inlineStr">
-        <is>
-          <t>Fontanería</t>
-        </is>
-      </c>
-      <c r="D12" s="11" t="n"/>
-      <c r="E12" s="12" t="n"/>
-      <c r="F12" s="11" t="n"/>
-      <c r="G12" s="13" t="n"/>
+      <c r="B12" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C12">
+        <f>COUNTIFS(B6:B11,"?*",E6:E11,"✓")-COUNTIFS(B6:B11,"Tarea",E6:E11,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E12">
+        <f>COUNTIF(B6:B11,"?*")-COUNTIF(B6:B11,"Tarea")-COUNTIF(E6:E11,"N/A")</f>
+        <v>6.0</v>
+      </c>
     </row>
     <row r="13">
-      <c r="B13" s="16" t="inlineStr">
-        <is>
-          <t>Tareas completadas:</t>
-        </is>
-      </c>
-      <c r="C13">
-        <f>COUNTIF(E6:E12,"✓")</f>
-        <v>0.0</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>de</t>
-        </is>
-      </c>
-      <c r="E13">
-        <f>COUNTIF(B6:B12,"?*")</f>
-        <v>7.0</v>
+      <c r="A13" s="14" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
-        <is>
-          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="14" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
@@ -2027,19 +2680,19 @@
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A4:G4"/>
-    <mergeCell ref="A15:G15"/>
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A14:G14"/>
+    <mergeCell ref="A13:G13"/>
   </mergeCells>
-  <conditionalFormatting sqref="A6:G12">
+  <conditionalFormatting sqref="A6:G11">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$E6="✓"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -2077,7 +2730,7 @@
     <row r="1">
       <c r="A1" s="4" t="inlineStr">
         <is>
-          <t>Electricidad — Control y Seguridad</t>
+          <t>Fontanería — Control y Prevención</t>
         </is>
       </c>
     </row>
@@ -2092,7 +2745,7 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Revisiones eléctricas</t>
+          <t>Revisiones de fontanería</t>
         </is>
       </c>
     </row>
@@ -2139,12 +2792,12 @@
       </c>
       <c r="B6" s="9" t="inlineStr">
         <is>
-          <t>Verificar cuadros secundarios por planta: sin disparos ni alarmas</t>
+          <t>Verificar presión de agua en puntos altos del edificio</t>
         </is>
       </c>
       <c r="C6" s="10" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Fontanería</t>
         </is>
       </c>
       <c r="D6" s="11" t="n"/>
@@ -2158,12 +2811,12 @@
       </c>
       <c r="B7" s="9" t="inlineStr">
         <is>
-          <t>Comprobar alumbrado de emergencia y señalización evacuación</t>
+          <t>Controlar temperatura de ACS para prevención de legionella (&gt;50 °C)</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Fontanería</t>
         </is>
       </c>
       <c r="D7" s="11" t="n"/>
@@ -2177,12 +2830,12 @@
       </c>
       <c r="B8" s="9" t="inlineStr">
         <is>
-          <t>Revisar luminarias LED: reemplazar fundidas, verificar reguladores</t>
+          <t>Inspeccionar cuartos técnicos: fugas, humedad, corrosión</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Fontanería</t>
         </is>
       </c>
       <c r="D8" s="11" t="n"/>
@@ -2196,12 +2849,12 @@
       </c>
       <c r="B9" s="9" t="inlineStr">
         <is>
-          <t>Verificar tomas de corriente en habitaciones y zonas comunes</t>
+          <t>Realizar desatascos preventivos en zonas de alto uso</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Fontanería</t>
         </is>
       </c>
       <c r="D9" s="11" t="n"/>
@@ -2215,12 +2868,12 @@
       </c>
       <c r="B10" s="9" t="inlineStr">
         <is>
-          <t>Comprobar cerraduras electrónicas: baterías, programación, backup</t>
+          <t>Verificar cisternas: consumo fantasma, mecanismo, flotador</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Fontanería</t>
         </is>
       </c>
       <c r="D10" s="11" t="n"/>
@@ -2234,12 +2887,12 @@
       </c>
       <c r="B11" s="9" t="inlineStr">
         <is>
-          <t>Verificar sistema de megafonía y música ambiental</t>
+          <t>Revisar grifería de habitaciones: goteos, cal, funcionamiento</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Fontanería</t>
         </is>
       </c>
       <c r="D11" s="11" t="n"/>
@@ -2253,12 +2906,12 @@
       </c>
       <c r="B12" s="9" t="inlineStr">
         <is>
-          <t>Comprobar cargadores de vehículos eléctricos si existen</t>
+          <t>Verificar radiadores/calefacción: purgado, fugas, termostatos</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
         <is>
-          <t>Electricidad</t>
+          <t>Fontanería</t>
         </is>
       </c>
       <c r="D12" s="11" t="n"/>
@@ -2273,7 +2926,7 @@
         </is>
       </c>
       <c r="C13">
-        <f>COUNTIF(E6:E12,"✓")</f>
+        <f>COUNTIFS(B6:B12,"?*",E6:E12,"✓")-COUNTIFS(B6:B12,"Tarea",E6:E12,"✓")</f>
         <v>0.0</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -2282,7 +2935,7 @@
         </is>
       </c>
       <c r="E13">
-        <f>COUNTIF(B6:B12,"?*")</f>
+        <f>COUNTIF(B6:B12,"?*")-COUNTIF(B6:B12,"Tarea")-COUNTIF(E6:E12,"N/A")</f>
         <v>7.0</v>
       </c>
     </row>
@@ -2314,8 +2967,284 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Usa ✓, ✗ o —" prompt="Marca ✓ si completada" type="list">
-      <formula1>"✓,✗,—"</formula1>
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFF3E0"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:G15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="5" customWidth="1" min="1" max="1"/>
+    <col width="45" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="15" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Electricidad — Control y Seguridad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Kit de Tareas: Hotel Integral</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Revisiones eléctricas</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Tarea</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Zona</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Responsable</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="F5" s="7" t="inlineStr">
+        <is>
+          <t>Hora</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="inlineStr">
+        <is>
+          <t>Notas</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="9" t="inlineStr">
+        <is>
+          <t>Verificar cuadros secundarios por planta: sin disparos ni alarmas</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>Electricidad</t>
+        </is>
+      </c>
+      <c r="D6" s="11" t="n"/>
+      <c r="E6" s="12" t="n"/>
+      <c r="F6" s="11" t="n"/>
+      <c r="G6" s="13" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="B7" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar alumbrado de emergencia y señalización evacuación</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>Electricidad</t>
+        </is>
+      </c>
+      <c r="D7" s="11" t="n"/>
+      <c r="E7" s="12" t="n"/>
+      <c r="F7" s="11" t="n"/>
+      <c r="G7" s="13" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="B8" s="9" t="inlineStr">
+        <is>
+          <t>Revisar luminarias LED: reemplazar fundidas, verificar reguladores</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
+        <is>
+          <t>Electricidad</t>
+        </is>
+      </c>
+      <c r="D8" s="11" t="n"/>
+      <c r="E8" s="12" t="n"/>
+      <c r="F8" s="11" t="n"/>
+      <c r="G8" s="13" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="B9" s="9" t="inlineStr">
+        <is>
+          <t>Verificar tomas de corriente en habitaciones y zonas comunes</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
+        <is>
+          <t>Electricidad</t>
+        </is>
+      </c>
+      <c r="D9" s="11" t="n"/>
+      <c r="E9" s="12" t="n"/>
+      <c r="F9" s="11" t="n"/>
+      <c r="G9" s="13" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="B10" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar cerraduras electrónicas: baterías, programación, backup</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
+        <is>
+          <t>Electricidad</t>
+        </is>
+      </c>
+      <c r="D10" s="11" t="n"/>
+      <c r="E10" s="12" t="n"/>
+      <c r="F10" s="11" t="n"/>
+      <c r="G10" s="13" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="B11" s="9" t="inlineStr">
+        <is>
+          <t>Verificar sistema de megafonía y música ambiental</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
+        <is>
+          <t>Electricidad</t>
+        </is>
+      </c>
+      <c r="D11" s="11" t="n"/>
+      <c r="E11" s="12" t="n"/>
+      <c r="F11" s="11" t="n"/>
+      <c r="G11" s="13" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="9" t="inlineStr">
+        <is>
+          <t>Comprobar cargadores de vehículos eléctricos si existen</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>Electricidad</t>
+        </is>
+      </c>
+      <c r="D12" s="11" t="n"/>
+      <c r="E12" s="12" t="n"/>
+      <c r="F12" s="11" t="n"/>
+      <c r="G12" s="13" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="16" t="inlineStr">
+        <is>
+          <t>Tareas completadas:</t>
+        </is>
+      </c>
+      <c r="C13">
+        <f>COUNTIFS(B6:B12,"?*",E6:E12,"✓")-COUNTIFS(B6:B12,"Tarea",E6:E12,"✓")</f>
+        <v>0.0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>de</t>
+        </is>
+      </c>
+      <c r="E13">
+        <f>COUNTIF(B6:B12,"?*")-COUNTIF(B6:B12,"Tarea")-COUNTIF(E6:E12,"N/A")</f>
+        <v>7.0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
+          <t>Firma responsable: _________________  Fecha: ___/___/______</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
+          <t>© 2026 AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A15:G15"/>
+    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A14:G14"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A6:G12">
+    <cfRule type="expression" priority="1" dxfId="0">
+      <formula>$E6="✓"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="E6 E7 E8 E9 E10 E11 E12" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Marca no válida" error="Usa el desplegable: ✓, — o N/A. N/A = no aplica, sale del total; — = no hecha, cuenta como pendiente." prompt="Marca ✓ si completada" type="list" errorStyle="stop">
+      <formula1>"✓,—,N/A"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>

--- a/astro-site/public/dl/kit-tareas-hotel/13-mantenimiento.xlsx
+++ b/astro-site/public/dl/kit-tareas-hotel/13-mantenimiento.xlsx
@@ -1602,7 +1602,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G42"/>
+  <dimension ref="A1:G39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -2414,14 +2414,11 @@
         </is>
       </c>
     </row>
-    <row r="40"/>
-    <row r="41"/>
-    <row r="42"/>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A4:G4"/>
+    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A1:G1"/>
-    <mergeCell ref="A12:G12"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A39:G39"/>
     <mergeCell ref="A19:G19"/>
